--- a/Daily_Report/Top 7 broker List with its Turnover 2024-07-14.xlsx
+++ b/Daily_Report/Top 7 broker List with its Turnover 2024-07-14.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="273">
   <si>
     <t>Date: 2024-07-14</t>
   </si>
@@ -74,12 +74,12 @@
     <t>Sumeru Securities Pvt.Limited</t>
   </si>
   <si>
+    <t>Linch Stock Market Limited</t>
+  </si>
+  <si>
     <t>Online Securities Pvt.Ltd</t>
   </si>
   <si>
-    <t>Linch Stock Market Limited</t>
-  </si>
-  <si>
     <t>58</t>
   </si>
   <si>
@@ -95,73 +95,73 @@
     <t>39</t>
   </si>
   <si>
+    <t>41</t>
+  </si>
+  <si>
     <t>49</t>
   </si>
   <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>847,248,323.55</t>
-  </si>
-  <si>
-    <t>644,237,106.58</t>
-  </si>
-  <si>
-    <t>576,956,803.11</t>
-  </si>
-  <si>
-    <t>541,051,191.5</t>
-  </si>
-  <si>
-    <t>505,244,896.1</t>
-  </si>
-  <si>
-    <t>488,905,536.84</t>
-  </si>
-  <si>
-    <t>486,339,241.5</t>
-  </si>
-  <si>
-    <t>451,495,006.7</t>
-  </si>
-  <si>
-    <t>348,698,526.81</t>
-  </si>
-  <si>
-    <t>317,392,051.54</t>
-  </si>
-  <si>
-    <t>279,379,897.5</t>
-  </si>
-  <si>
-    <t>220,301,610.0</t>
-  </si>
-  <si>
-    <t>236,125,577.49</t>
-  </si>
-  <si>
-    <t>230,438,752.5</t>
-  </si>
-  <si>
-    <t>395,753,316.85</t>
-  </si>
-  <si>
-    <t>295,538,579.77</t>
-  </si>
-  <si>
-    <t>259,564,751.57</t>
-  </si>
-  <si>
-    <t>261,671,294.0</t>
-  </si>
-  <si>
-    <t>284,943,286.1</t>
-  </si>
-  <si>
-    <t>252,779,959.35</t>
-  </si>
-  <si>
-    <t>255,900,489.0</t>
+    <t>843,736,002.95</t>
+  </si>
+  <si>
+    <t>608,504,060.69</t>
+  </si>
+  <si>
+    <t>548,742,899.21</t>
+  </si>
+  <si>
+    <t>540,482,254.4</t>
+  </si>
+  <si>
+    <t>504,822,929.8</t>
+  </si>
+  <si>
+    <t>499,678,688.0</t>
+  </si>
+  <si>
+    <t>499,464,452.94</t>
+  </si>
+  <si>
+    <t>477,371,467.6</t>
+  </si>
+  <si>
+    <t>323,573,334.41</t>
+  </si>
+  <si>
+    <t>296,722,620.24</t>
+  </si>
+  <si>
+    <t>292,108,572.5</t>
+  </si>
+  <si>
+    <t>219,971,267.5</t>
+  </si>
+  <si>
+    <t>235,308,634.5</t>
+  </si>
+  <si>
+    <t>238,518,644.49</t>
+  </si>
+  <si>
+    <t>366,364,535.35</t>
+  </si>
+  <si>
+    <t>284,930,726.27</t>
+  </si>
+  <si>
+    <t>252,020,278.97</t>
+  </si>
+  <si>
+    <t>248,373,681.9</t>
+  </si>
+  <si>
+    <t>284,851,662.3</t>
+  </si>
+  <si>
+    <t>264,370,053.5</t>
+  </si>
+  <si>
+    <t>260,945,808.45</t>
   </si>
   <si>
     <t>Top 5 Buy</t>
@@ -182,7 +182,13 @@
     <t>SHINE</t>
   </si>
   <si>
-    <t>37,246,401.79</t>
+    <t>37,287,401.79</t>
+  </si>
+  <si>
+    <t>NRN</t>
+  </si>
+  <si>
+    <t>32,235,036.2</t>
   </si>
   <si>
     <t>SPIL</t>
@@ -191,67 +197,52 @@
     <t>29,410,996.9</t>
   </si>
   <si>
-    <t>NRN</t>
-  </si>
-  <si>
-    <t>28,756,195.2</t>
-  </si>
-  <si>
     <t>JFL</t>
   </si>
   <si>
-    <t>17,927,929.3</t>
-  </si>
-  <si>
-    <t>MMKJL</t>
-  </si>
-  <si>
-    <t>14,094,842.6</t>
-  </si>
-  <si>
-    <t>JBLB</t>
-  </si>
-  <si>
-    <t>21,384,438.0</t>
+    <t>17,726,889.3</t>
+  </si>
+  <si>
+    <t>GMFBS</t>
+  </si>
+  <si>
+    <t>16,543,574.2</t>
   </si>
   <si>
     <t>SGIC</t>
   </si>
   <si>
-    <t>18,186,865.0</t>
-  </si>
-  <si>
-    <t>NIMB</t>
-  </si>
-  <si>
-    <t>7,497,235.4</t>
+    <t>10,672,995.0</t>
   </si>
   <si>
     <t>HRL</t>
   </si>
   <si>
-    <t>7,373,689.4</t>
+    <t>7,211,189.4</t>
+  </si>
+  <si>
+    <t>GBIME</t>
+  </si>
+  <si>
+    <t>7,189,941.7</t>
   </si>
   <si>
     <t>SHEL</t>
   </si>
   <si>
-    <t>7,036,998.3</t>
-  </si>
-  <si>
-    <t>SAPDBL</t>
-  </si>
-  <si>
-    <t>21,461,406.0</t>
-  </si>
-  <si>
-    <t>13,329,671.5</t>
+    <t>7,070,598.3</t>
+  </si>
+  <si>
+    <t>6,930,831.8</t>
+  </si>
+  <si>
+    <t>11,336,371.5</t>
   </si>
   <si>
     <t>PCBL</t>
   </si>
   <si>
-    <t>11,167,605.1</t>
+    <t>9,889,155.1</t>
   </si>
   <si>
     <t>USHEC</t>
@@ -260,34 +251,40 @@
     <t>9,414,001.4</t>
   </si>
   <si>
+    <t>8,909,379.19</t>
+  </si>
+  <si>
+    <t>HDL</t>
+  </si>
+  <si>
+    <t>7,289,429.2</t>
+  </si>
+  <si>
     <t>NFS</t>
   </si>
   <si>
-    <t>8,377,662.3</t>
-  </si>
-  <si>
-    <t>20,322,495.1</t>
+    <t>22,038,955.1</t>
   </si>
   <si>
     <t>CLI</t>
   </si>
   <si>
-    <t>11,666,240.0</t>
+    <t>12,317,040.0</t>
   </si>
   <si>
     <t>KBL</t>
   </si>
   <si>
-    <t>9,666,832.0</t>
-  </si>
-  <si>
-    <t>9,016,917.5</t>
-  </si>
-  <si>
-    <t>MEN</t>
-  </si>
-  <si>
-    <t>7,692,773.0</t>
+    <t>9,835,897.0</t>
+  </si>
+  <si>
+    <t>9,649,978.5</t>
+  </si>
+  <si>
+    <t>NABIL</t>
+  </si>
+  <si>
+    <t>6,476,336.5</t>
   </si>
   <si>
     <t>GBIMEP</t>
@@ -299,10 +296,10 @@
     <t>CHDC</t>
   </si>
   <si>
-    <t>18,570,900.2</t>
-  </si>
-  <si>
-    <t>6,171,902.0</t>
+    <t>19,641,600.2</t>
+  </si>
+  <si>
+    <t>6,187,100.0</t>
   </si>
   <si>
     <t>5,476,559.8</t>
@@ -314,13 +311,31 @@
     <t>3,798,166.0</t>
   </si>
   <si>
+    <t>72,844,324.9</t>
+  </si>
+  <si>
+    <t>29,664,327.4</t>
+  </si>
+  <si>
+    <t>5,587,730.0</t>
+  </si>
+  <si>
+    <t>HLI</t>
+  </si>
+  <si>
+    <t>5,090,313.09</t>
+  </si>
+  <si>
+    <t>4,436,057.0</t>
+  </si>
+  <si>
     <t>NRIC</t>
   </si>
   <si>
-    <t>17,115,855.3</t>
-  </si>
-  <si>
-    <t>11,166,979.4</t>
+    <t>17,606,360.3</t>
+  </si>
+  <si>
+    <t>11,247,879.4</t>
   </si>
   <si>
     <t>HEI</t>
@@ -329,31 +344,10 @@
     <t>9,222,144.19</t>
   </si>
   <si>
-    <t>AKPL</t>
-  </si>
-  <si>
-    <t>5,609,425.8</t>
-  </si>
-  <si>
-    <t>5,535,087.3</t>
-  </si>
-  <si>
-    <t>73,456,642.9</t>
-  </si>
-  <si>
-    <t>29,664,327.4</t>
-  </si>
-  <si>
-    <t>7,288,952.4</t>
-  </si>
-  <si>
-    <t>3,799,730.0</t>
-  </si>
-  <si>
-    <t>HDL</t>
-  </si>
-  <si>
-    <t>3,739,069.0</t>
+    <t>5,796,168.3</t>
+  </si>
+  <si>
+    <t>5,557,287.3</t>
   </si>
   <si>
     <t>Sell Amount</t>
@@ -362,85 +356,70 @@
     <t>24,497,963.2</t>
   </si>
   <si>
+    <t>SADBL</t>
+  </si>
+  <si>
+    <t>13,335,965.8</t>
+  </si>
+  <si>
+    <t>13,065,075.2</t>
+  </si>
+  <si>
+    <t>MFIL</t>
+  </si>
+  <si>
+    <t>12,544,431.0</t>
+  </si>
+  <si>
+    <t>NGPL</t>
+  </si>
+  <si>
+    <t>10,572,126.69</t>
+  </si>
+  <si>
+    <t>13,381,074.6</t>
+  </si>
+  <si>
+    <t>TAMOR</t>
+  </si>
+  <si>
+    <t>8,889,676.0</t>
+  </si>
+  <si>
+    <t>AHPC</t>
+  </si>
+  <si>
+    <t>7,564,261.2</t>
+  </si>
+  <si>
+    <t>EBL</t>
+  </si>
+  <si>
+    <t>6,003,744.0</t>
+  </si>
+  <si>
+    <t>MERO</t>
+  </si>
+  <si>
+    <t>5,952,165.9</t>
+  </si>
+  <si>
+    <t>12,246,135.8</t>
+  </si>
+  <si>
+    <t>11,264,270.0</t>
+  </si>
+  <si>
+    <t>8,544,296.8</t>
+  </si>
+  <si>
     <t>RIDI</t>
   </si>
   <si>
-    <t>21,046,025.8</t>
-  </si>
-  <si>
-    <t>SADBL</t>
-  </si>
-  <si>
-    <t>13,335,965.8</t>
-  </si>
-  <si>
-    <t>AHPC</t>
-  </si>
-  <si>
-    <t>13,087,707.6</t>
-  </si>
-  <si>
-    <t>GMFBS</t>
-  </si>
-  <si>
-    <t>13,065,075.2</t>
-  </si>
-  <si>
-    <t>13,229,274.6</t>
-  </si>
-  <si>
-    <t>NICLBSL</t>
-  </si>
-  <si>
-    <t>10,150,583.1</t>
-  </si>
-  <si>
-    <t>TAMOR</t>
-  </si>
-  <si>
-    <t>8,889,676.0</t>
-  </si>
-  <si>
-    <t>6,944,999.2</t>
-  </si>
-  <si>
-    <t>SONA</t>
-  </si>
-  <si>
-    <t>6,234,447.4</t>
-  </si>
-  <si>
-    <t>12,246,135.8</t>
-  </si>
-  <si>
-    <t>HPPL</t>
-  </si>
-  <si>
-    <t>12,130,916.5</t>
-  </si>
-  <si>
-    <t>10,690,761.6</t>
-  </si>
-  <si>
-    <t>NICA</t>
-  </si>
-  <si>
-    <t>7,985,089.6</t>
-  </si>
-  <si>
-    <t>7,400,477.3</t>
-  </si>
-  <si>
-    <t>NABIL</t>
-  </si>
-  <si>
-    <t>15,913,976.4</t>
-  </si>
-  <si>
-    <t>MANDU</t>
-  </si>
-  <si>
-    <t>13,976,424.0</t>
+    <t>7,402,180.3</t>
+  </si>
+  <si>
+    <t>7,262,195.6</t>
   </si>
   <si>
     <t>VLBS</t>
@@ -458,54 +437,66 @@
     <t>5,989,216.0</t>
   </si>
   <si>
+    <t>UMRH</t>
+  </si>
+  <si>
+    <t>5,927,885.3</t>
+  </si>
+  <si>
+    <t>SARBTM</t>
+  </si>
+  <si>
+    <t>5,499,098.4</t>
+  </si>
+  <si>
     <t>21,217,207.5</t>
   </si>
   <si>
     <t>18,026,516.8</t>
   </si>
   <si>
-    <t>12,249,488.9</t>
+    <t>12,323,128.9</t>
   </si>
   <si>
     <t>11,860,861.0</t>
   </si>
   <si>
-    <t>14,638,079.7</t>
-  </si>
-  <si>
-    <t>8,258,223.5</t>
+    <t>130,945,174.9</t>
+  </si>
+  <si>
+    <t>18,225,920.3</t>
+  </si>
+  <si>
+    <t>9,311,888.4</t>
+  </si>
+  <si>
+    <t>GFCL</t>
+  </si>
+  <si>
+    <t>7,576,865.5</t>
+  </si>
+  <si>
+    <t>5,632,799.0</t>
+  </si>
+  <si>
+    <t>14,924,745.9</t>
+  </si>
+  <si>
+    <t>8,330,703.5</t>
+  </si>
+  <si>
+    <t>7,701,362.6</t>
   </si>
   <si>
     <t>LSL</t>
   </si>
   <si>
-    <t>7,805,007.0</t>
-  </si>
-  <si>
-    <t>7,701,362.6</t>
+    <t>7,199,507.0</t>
   </si>
   <si>
     <t>6,671,814.3</t>
   </si>
   <si>
-    <t>130,636,609.9</t>
-  </si>
-  <si>
-    <t>18,225,920.3</t>
-  </si>
-  <si>
-    <t>9,270,728.4</t>
-  </si>
-  <si>
-    <t>GFCL</t>
-  </si>
-  <si>
-    <t>7,311,065.5</t>
-  </si>
-  <si>
-    <t>5,558,299.0</t>
-  </si>
-  <si>
     <t>Top Traded Stocks</t>
   </si>
   <si>
@@ -521,103 +512,103 @@
     <t>Percentage (%)</t>
   </si>
   <si>
-    <t>237,454,478.0</t>
+    <t>242,758,572.5</t>
+  </si>
+  <si>
+    <t>212,747,749.3</t>
   </si>
   <si>
     <t>207,510,200.0</t>
   </si>
   <si>
-    <t>201,062,341.8</t>
-  </si>
-  <si>
-    <t>190,774,594.8</t>
-  </si>
-  <si>
-    <t>149,101,667.0</t>
+    <t>191,719,593.3</t>
+  </si>
+  <si>
+    <t>151,485,419.0</t>
   </si>
   <si>
     <t>Promoter Shares/debenture</t>
   </si>
   <si>
-    <t>2,158,405,471.12</t>
+    <t>2,151,591,487.32</t>
   </si>
   <si>
     <t>Hydro Power</t>
   </si>
   <si>
-    <t>1,554,453,005.3</t>
+    <t>1,579,485,218.8</t>
   </si>
   <si>
     <t>Finance</t>
   </si>
   <si>
-    <t>836,363,930.9</t>
+    <t>840,765,115.3</t>
   </si>
   <si>
     <t>Microfinance</t>
   </si>
   <si>
-    <t>719,112,348.8</t>
+    <t>662,638,469.0</t>
   </si>
   <si>
     <t>Commercial Banks</t>
   </si>
   <si>
-    <t>605,897,040.7</t>
+    <t>617,629,061.0</t>
+  </si>
+  <si>
+    <t>Investment</t>
+  </si>
+  <si>
+    <t>500,398,636.9</t>
   </si>
   <si>
     <t>Development Banks</t>
   </si>
   <si>
-    <t>505,070,212.0</t>
-  </si>
-  <si>
-    <t>Investment</t>
-  </si>
-  <si>
-    <t>479,488,267.8</t>
+    <t>495,543,513.3</t>
   </si>
   <si>
     <t>Manufacturing And Processing</t>
   </si>
   <si>
-    <t>213,760,884.4</t>
+    <t>219,932,405.9</t>
   </si>
   <si>
     <t>Non Life Insurance</t>
   </si>
   <si>
-    <t>205,656,852.6</t>
+    <t>203,515,968.2</t>
   </si>
   <si>
     <t>Life Insurance</t>
   </si>
   <si>
-    <t>134,833,091.1</t>
+    <t>139,146,986.69</t>
   </si>
   <si>
     <t>Others</t>
   </si>
   <si>
-    <t>91,013,222.0</t>
+    <t>92,594,974.0</t>
   </si>
   <si>
     <t>Hotels And Tourism</t>
   </si>
   <si>
-    <t>79,053,778.8</t>
+    <t>79,891,094.59</t>
   </si>
   <si>
     <t>Trading</t>
   </si>
   <si>
-    <t>20,952,052.6</t>
+    <t>20,850,586.6</t>
   </si>
   <si>
     <t>Mutual Fund</t>
   </si>
   <si>
-    <t>15,304,147.75</t>
+    <t>14,646,133.75</t>
   </si>
   <si>
     <t>Tradings</t>
@@ -635,214 +626,214 @@
     <t>100%</t>
   </si>
   <si>
-    <t>130,479,794.7</t>
-  </si>
-  <si>
-    <t>71,258,398.5</t>
-  </si>
-  <si>
-    <t>70,710,265.2</t>
-  </si>
-  <si>
-    <t>41,162,399.9</t>
-  </si>
-  <si>
-    <t>37,486,023.5</t>
-  </si>
-  <si>
-    <t>97,116,099.61</t>
-  </si>
-  <si>
-    <t>76,243,608.0</t>
-  </si>
-  <si>
-    <t>45,835,811.6</t>
-  </si>
-  <si>
-    <t>38,044,045.5</t>
-  </si>
-  <si>
-    <t>33,604,324.9</t>
-  </si>
-  <si>
-    <t>74,460,804.59</t>
-  </si>
-  <si>
-    <t>70,525,352.0</t>
-  </si>
-  <si>
-    <t>38,887,042.29</t>
-  </si>
-  <si>
-    <t>36,370,254.9</t>
-  </si>
-  <si>
-    <t>31,945,605.3</t>
-  </si>
-  <si>
-    <t>75,170,654.9</t>
-  </si>
-  <si>
-    <t>64,648,391.9</t>
-  </si>
-  <si>
-    <t>39,526,491.79</t>
-  </si>
-  <si>
-    <t>27,826,151.2</t>
-  </si>
-  <si>
-    <t>17,280,922.1</t>
-  </si>
-  <si>
-    <t>122,374,967.2</t>
-  </si>
-  <si>
-    <t>29,580,302.7</t>
-  </si>
-  <si>
-    <t>28,122,046.1</t>
-  </si>
-  <si>
-    <t>11,048,826.1</t>
-  </si>
-  <si>
-    <t>9,861,350.4</t>
-  </si>
-  <si>
-    <t>50,317,602.8</t>
-  </si>
-  <si>
-    <t>40,805,862.4</t>
-  </si>
-  <si>
-    <t>30,066,904.3</t>
-  </si>
-  <si>
-    <t>21,357,920.8</t>
-  </si>
-  <si>
-    <t>17,990,432.3</t>
-  </si>
-  <si>
-    <t>111,893,538.8</t>
-  </si>
-  <si>
-    <t>40,113,790.29</t>
-  </si>
-  <si>
-    <t>28,545,447.7</t>
-  </si>
-  <si>
-    <t>11,383,669.1</t>
-  </si>
-  <si>
-    <t>9,128,675.6</t>
-  </si>
-  <si>
-    <t>117,244,416.5</t>
-  </si>
-  <si>
-    <t>60,695,381.2</t>
-  </si>
-  <si>
-    <t>53,935,945.8</t>
-  </si>
-  <si>
-    <t>51,511,020.5</t>
-  </si>
-  <si>
-    <t>45,618,172.2</t>
-  </si>
-  <si>
-    <t>77,623,112.4</t>
-  </si>
-  <si>
-    <t>55,973,751.4</t>
-  </si>
-  <si>
-    <t>38,728,593.6</t>
-  </si>
-  <si>
-    <t>28,870,779.1</t>
-  </si>
-  <si>
-    <t>24,019,407.3</t>
-  </si>
-  <si>
-    <t>78,638,767.09</t>
-  </si>
-  <si>
-    <t>71,334,791.67</t>
-  </si>
-  <si>
-    <t>28,783,202.4</t>
-  </si>
-  <si>
-    <t>21,130,991.8</t>
-  </si>
-  <si>
-    <t>11,917,705.5</t>
-  </si>
-  <si>
-    <t>70,778,371.0</t>
-  </si>
-  <si>
-    <t>61,397,043.0</t>
-  </si>
-  <si>
-    <t>38,971,974.9</t>
-  </si>
-  <si>
-    <t>26,907,328.1</t>
-  </si>
-  <si>
-    <t>20,167,841.39</t>
-  </si>
-  <si>
-    <t>126,925,280.1</t>
+    <t>148,981,903.3</t>
+  </si>
+  <si>
+    <t>73,501,118.59</t>
+  </si>
+  <si>
+    <t>71,869,807.5</t>
+  </si>
+  <si>
+    <t>42,165,736.9</t>
+  </si>
+  <si>
+    <t>36,378,057.0</t>
+  </si>
+  <si>
+    <t>86,806,699.11</t>
+  </si>
+  <si>
+    <t>75,738,085.09</t>
+  </si>
+  <si>
+    <t>38,052,898.5</t>
+  </si>
+  <si>
+    <t>35,348,690.9</t>
+  </si>
+  <si>
+    <t>26,678,284.6</t>
+  </si>
+  <si>
+    <t>75,616,846.7</t>
+  </si>
+  <si>
+    <t>67,817,652.8</t>
+  </si>
+  <si>
+    <t>39,174,485.29</t>
+  </si>
+  <si>
+    <t>36,424,823.9</t>
+  </si>
+  <si>
+    <t>24,588,673.5</t>
+  </si>
+  <si>
+    <t>79,706,767.8</t>
+  </si>
+  <si>
+    <t>63,644,752.2</t>
+  </si>
+  <si>
+    <t>42,357,342.79</t>
+  </si>
+  <si>
+    <t>31,239,489.8</t>
+  </si>
+  <si>
+    <t>15,482,544.1</t>
+  </si>
+  <si>
+    <t>122,774,017.2</t>
+  </si>
+  <si>
+    <t>30,783,900.7</t>
+  </si>
+  <si>
+    <t>28,416,671.6</t>
+  </si>
+  <si>
+    <t>11,219,026.1</t>
+  </si>
+  <si>
+    <t>8,052,058.4</t>
+  </si>
+  <si>
+    <t>111,911,200.8</t>
+  </si>
+  <si>
+    <t>37,580,268.79</t>
+  </si>
+  <si>
+    <t>30,123,380.2</t>
+  </si>
+  <si>
+    <t>12,791,501.1</t>
+  </si>
+  <si>
+    <t>9,615,111.6</t>
+  </si>
+  <si>
+    <t>48,759,568.8</t>
+  </si>
+  <si>
+    <t>44,281,898.4</t>
+  </si>
+  <si>
+    <t>26,763,561.3</t>
+  </si>
+  <si>
+    <t>23,891,260.8</t>
+  </si>
+  <si>
+    <t>18,567,847.3</t>
+  </si>
+  <si>
+    <t>95,701,633.6</t>
+  </si>
+  <si>
+    <t>60,281,377.1</t>
+  </si>
+  <si>
+    <t>52,592,293.0</t>
+  </si>
+  <si>
+    <t>44,469,406.8</t>
+  </si>
+  <si>
+    <t>43,081,338.2</t>
+  </si>
+  <si>
+    <t>76,225,369.7</t>
+  </si>
+  <si>
+    <t>60,252,479.9</t>
+  </si>
+  <si>
+    <t>30,270,319.6</t>
+  </si>
+  <si>
+    <t>29,458,502.6</t>
+  </si>
+  <si>
+    <t>25,283,686.3</t>
+  </si>
+  <si>
+    <t>72,860,282.27</t>
+  </si>
+  <si>
+    <t>70,124,822.2</t>
+  </si>
+  <si>
+    <t>23,754,612.8</t>
+  </si>
+  <si>
+    <t>22,285,001.2</t>
+  </si>
+  <si>
+    <t>13,943,343.0</t>
+  </si>
+  <si>
+    <t>65,759,328.5</t>
+  </si>
+  <si>
+    <t>64,556,473.4</t>
+  </si>
+  <si>
+    <t>39,554,861.9</t>
+  </si>
+  <si>
+    <t>21,518,246.4</t>
+  </si>
+  <si>
+    <t>15,348,037.1</t>
+  </si>
+  <si>
+    <t>127,818,789.6</t>
   </si>
   <si>
     <t>51,178,218.1</t>
   </si>
   <si>
-    <t>31,580,711.9</t>
-  </si>
-  <si>
-    <t>22,205,129.7</t>
-  </si>
-  <si>
-    <t>15,908,884.5</t>
-  </si>
-  <si>
-    <t>70,440,267.45</t>
-  </si>
-  <si>
-    <t>58,036,518.0</t>
-  </si>
-  <si>
-    <t>28,283,115.1</t>
-  </si>
-  <si>
-    <t>20,212,697.5</t>
-  </si>
-  <si>
-    <t>16,072,041.7</t>
-  </si>
-  <si>
-    <t>161,376,241.1</t>
-  </si>
-  <si>
-    <t>30,529,666.7</t>
-  </si>
-  <si>
-    <t>26,376,316.2</t>
-  </si>
-  <si>
-    <t>9,933,701.6</t>
-  </si>
-  <si>
-    <t>8,138,131.1</t>
+    <t>30,852,158.0</t>
+  </si>
+  <si>
+    <t>23,446,983.7</t>
+  </si>
+  <si>
+    <t>15,712,657.5</t>
+  </si>
+  <si>
+    <t>161,984,180.1</t>
+  </si>
+  <si>
+    <t>30,503,577.2</t>
+  </si>
+  <si>
+    <t>29,122,117.5</t>
+  </si>
+  <si>
+    <t>10,706,295.6</t>
+  </si>
+  <si>
+    <t>8,481,053.1</t>
+  </si>
+  <si>
+    <t>71,299,526.25</t>
+  </si>
+  <si>
+    <t>59,519,732.8</t>
+  </si>
+  <si>
+    <t>29,672,572.9</t>
+  </si>
+  <si>
+    <t>19,950,522.5</t>
+  </si>
+  <si>
+    <t>16,489,342.9</t>
   </si>
 </sst>
 </file>
@@ -1651,7 +1642,7 @@
         <v>55</v>
       </c>
       <c r="D9" s="10">
-        <v>0.04396161168420644</v>
+        <v>0.04419320933281266</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>64</v>
@@ -1660,52 +1651,52 @@
         <v>65</v>
       </c>
       <c r="G9" s="12">
-        <v>0.03319342798056075</v>
+        <v>0.01753972683090658</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="J9" s="14">
-        <v>0.03719759587600922</v>
+        <v>0.02065880308669224</v>
       </c>
       <c r="K9" s="15" t="s">
         <v>81</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M9" s="16">
-        <v>0.03756113177323998</v>
+        <v>0.0407764638349984</v>
       </c>
       <c r="N9" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="O9" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="O9" s="17" t="s">
-        <v>92</v>
-      </c>
       <c r="P9" s="18">
-        <v>0.2053560576284661</v>
+        <v>0.2055277085791359</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>99</v>
+        <v>60</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="S9" s="16">
-        <v>0.03500851189092048</v>
+        <v>0.1457823330259785</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>60</v>
+        <v>104</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="V9" s="18">
-        <v>0.1510399256976264</v>
+        <v>0.03525047717883344</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1717,7 +1708,7 @@
         <v>57</v>
       </c>
       <c r="D10" s="10">
-        <v>0.03471354983243508</v>
+        <v>0.03820512113658169</v>
       </c>
       <c r="E10" s="11" t="s">
         <v>66</v>
@@ -1726,52 +1717,52 @@
         <v>67</v>
       </c>
       <c r="G10" s="12">
-        <v>0.02823007990996448</v>
+        <v>0.01185068410525154</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J10" s="14">
-        <v>0.02310341333726959</v>
+        <v>0.01802147255889227</v>
       </c>
       <c r="K10" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="L10" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="L10" s="15" t="s">
-        <v>85</v>
-      </c>
       <c r="M10" s="16">
-        <v>0.02156217412192872</v>
+        <v>0.02278898132127093</v>
       </c>
       <c r="N10" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="O10" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="O10" s="17" t="s">
-        <v>94</v>
-      </c>
       <c r="P10" s="18">
-        <v>0.03675623513141709</v>
+        <v>0.03890790025679217</v>
       </c>
       <c r="Q10" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="R10" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="S10" s="16">
+        <v>0.05936680533391089</v>
+      </c>
+      <c r="T10" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="R10" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="S10" s="16">
-        <v>0.02284077098446632</v>
-      </c>
-      <c r="T10" s="17" t="s">
-        <v>81</v>
-      </c>
       <c r="U10" s="17" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="V10" s="18">
-        <v>0.06099513440146696</v>
+        <v>0.02251987971074128</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1783,7 +1774,7 @@
         <v>59</v>
       </c>
       <c r="D11" s="10">
-        <v>0.03394069294762431</v>
+        <v>0.03485805607105627</v>
       </c>
       <c r="E11" s="11" t="s">
         <v>68</v>
@@ -1792,52 +1783,52 @@
         <v>69</v>
       </c>
       <c r="G11" s="12">
-        <v>0.01163738524730978</v>
+        <v>0.0118157661788602</v>
       </c>
       <c r="H11" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="I11" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="I11" s="13" t="s">
-        <v>78</v>
-      </c>
       <c r="J11" s="14">
-        <v>0.01935605064331105</v>
+        <v>0.01715557761850387</v>
       </c>
       <c r="K11" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="L11" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="L11" s="15" t="s">
-        <v>87</v>
-      </c>
       <c r="M11" s="16">
-        <v>0.01786676039507437</v>
+        <v>0.01819837176878087</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P11" s="18">
-        <v>0.01221566422073947</v>
+        <v>0.01225598053252295</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="S11" s="16">
-        <v>0.01886283444365665</v>
+        <v>0.01118264623685531</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>70</v>
+        <v>107</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="V11" s="18">
-        <v>0.01498738283490949</v>
+        <v>0.01846406515161519</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1849,7 +1840,7 @@
         <v>61</v>
       </c>
       <c r="D12" s="10">
-        <v>0.02116018267806226</v>
+        <v>0.02100999511460992</v>
       </c>
       <c r="E12" s="11" t="s">
         <v>70</v>
@@ -1858,52 +1849,52 @@
         <v>71</v>
       </c>
       <c r="G12" s="12">
-        <v>0.01144561423825701</v>
+        <v>0.01161964028963496</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="J12" s="14">
-        <v>0.01631664857621095</v>
+        <v>0.016235980844265</v>
       </c>
       <c r="K12" s="15" t="s">
         <v>60</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="M12" s="16">
-        <v>0.01666555335549982</v>
+        <v>0.01785438545195648</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P12" s="18">
-        <v>0.01083941637466053</v>
+        <v>0.01084847671671668</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="S12" s="16">
-        <v>0.01147343479940124</v>
+        <v>0.0101871727216831</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="V12" s="18">
-        <v>0.007812920849817957</v>
+        <v>0.01160476639705186</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1915,61 +1906,61 @@
         <v>63</v>
       </c>
       <c r="D13" s="10">
-        <v>0.01663602300319949</v>
+        <v>0.01960752432296098</v>
       </c>
       <c r="E13" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="F13" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="F13" s="11" t="s">
-        <v>73</v>
-      </c>
       <c r="G13" s="12">
-        <v>0.0109229943882733</v>
+        <v>0.01138995160055453</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J13" s="14">
-        <v>0.01452043247404564</v>
+        <v>0.01328386975119725</v>
       </c>
       <c r="K13" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="L13" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="L13" s="15" t="s">
-        <v>90</v>
-      </c>
       <c r="M13" s="16">
-        <v>0.01421819805751227</v>
+        <v>0.01198251459187963</v>
       </c>
       <c r="N13" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="O13" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="O13" s="17" t="s">
-        <v>98</v>
-      </c>
       <c r="P13" s="18">
-        <v>0.007517475246792502</v>
+        <v>0.007523758878196661</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="S13" s="16">
-        <v>0.01132138395440472</v>
+        <v>0.008877819099621076</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>111</v>
+        <v>74</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="V13" s="18">
-        <v>0.007688191042260364</v>
+        <v>0.01112649212028627</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1980,7 +1971,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -1989,7 +1980,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -1998,7 +1989,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -2007,7 +1998,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -2016,7 +2007,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -2025,7 +2016,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -2034,7 +2025,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -2046,336 +2037,336 @@
         <v>54</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D16" s="10">
-        <v>0.02891473788623468</v>
+        <v>0.02903510471799999</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G16" s="12">
-        <v>0.02053479140626289</v>
+        <v>0.02199011553813925</v>
       </c>
       <c r="H16" s="13" t="s">
         <v>54</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="J16" s="14">
-        <v>0.02122539457718329</v>
+        <v>0.02231670936905097</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="M16" s="16">
-        <v>0.02941306968732551</v>
+        <v>0.02167368845995548</v>
       </c>
       <c r="N16" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="O16" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="O16" s="17" t="s">
-        <v>92</v>
-      </c>
       <c r="P16" s="18">
-        <v>0.2053560576284661</v>
+        <v>0.2055277085791359</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>99</v>
+        <v>60</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="S16" s="16">
-        <v>0.02994050710616206</v>
+        <v>0.2620587550454023</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>60</v>
+        <v>104</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="V16" s="18">
-        <v>0.268612110133416</v>
+        <v>0.02988149769647949</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D17" s="10">
-        <v>0.02484044549278825</v>
+        <v>0.01580585130108558</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G17" s="12">
-        <v>0.01575597399803292</v>
+        <v>0.01460906602647769</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>132</v>
+        <v>66</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="J17" s="14">
-        <v>0.02102569279816114</v>
+        <v>0.02052740913133756</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="M17" s="16">
-        <v>0.02583198081729019</v>
+        <v>0.0152338675931929</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="P17" s="18">
-        <v>0.04199390763524034</v>
+        <v>0.042029009079294</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="S17" s="16">
-        <v>0.01689124560416381</v>
+        <v>0.03647528049065003</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="V17" s="18">
-        <v>0.03747573451771319</v>
+        <v>0.01667927207024032</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>117</v>
+        <v>62</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D18" s="10">
-        <v>0.01574032716184299</v>
+        <v>0.01548479044905026</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G18" s="12">
-        <v>0.01379876431994703</v>
+        <v>0.01243091326526674</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="J18" s="14">
-        <v>0.01852957022496838</v>
+        <v>0.0155706740120024</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>142</v>
+        <v>56</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="M18" s="16">
-        <v>0.02165089770438108</v>
+        <v>0.01108124448350066</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="P18" s="18">
-        <v>0.03567877070930792</v>
+        <v>0.03570859352038886</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>153</v>
+        <v>66</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="S18" s="16">
-        <v>0.01596424342102364</v>
+        <v>0.01863575258186717</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="V18" s="18">
-        <v>0.01906226684773904</v>
+        <v>0.01541924065800365</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D19" s="10">
-        <v>0.01544731011701746</v>
+        <v>0.01486772041982353</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G19" s="12">
-        <v>0.0107801912199073</v>
+        <v>0.009866399236830374</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="J19" s="14">
-        <v>0.01384001290383883</v>
+        <v>0.01348934138493014</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M19" s="16">
-        <v>0.01521784856840113</v>
+        <v>0.01096777045266854</v>
       </c>
       <c r="N19" s="17" t="s">
         <v>60</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="P19" s="18">
-        <v>0.02424465639248246</v>
+        <v>0.0244107947015841</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>77</v>
+        <v>151</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="S19" s="16">
-        <v>0.01575225073084079</v>
+        <v>0.01516347541322395</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="V19" s="18">
-        <v>0.01503285130241747</v>
+        <v>0.01441445323610421</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D20" s="10">
-        <v>0.01542059728753063</v>
+        <v>0.0125301358043702</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G20" s="12">
-        <v>0.009677255991973893</v>
+        <v>0.009781637107319663</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="J20" s="14">
-        <v>0.01282674415157049</v>
+        <v>0.01323424068075423</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>58</v>
+        <v>142</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="M20" s="16">
-        <v>0.01106959210901211</v>
+        <v>0.01017442914218277</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="P20" s="18">
-        <v>0.02347546920622916</v>
+        <v>0.02349509164470603</v>
       </c>
       <c r="Q20" s="15" t="s">
         <v>56</v>
       </c>
       <c r="R20" s="15" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="S20" s="16">
-        <v>0.01364642818963089</v>
+        <v>0.01127284219894525</v>
       </c>
       <c r="T20" s="17" t="s">
         <v>58</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="V20" s="18">
-        <v>0.01142885156224845</v>
+        <v>0.01335793620692657</v>
       </c>
     </row>
     <row r="23" spans="1:22">
       <c r="B23" s="19" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -2383,23 +2374,23 @@
         <v>60</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="25" spans="1:22">
       <c r="B25" s="20" t="s">
-        <v>91</v>
+        <v>56</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="26" spans="1:22">
       <c r="B26" s="20" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -2407,188 +2398,188 @@
         <v>81</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="28" spans="1:22">
       <c r="B28" s="20" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="B30" s="19" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="31" spans="1:22">
       <c r="B31" s="20" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D31" s="22">
-        <v>0.2832367810595132</v>
+        <v>0.2823426159623953</v>
       </c>
     </row>
     <row r="32" spans="1:22">
       <c r="B32" s="20" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D32" s="22">
-        <v>0.2039831122652767</v>
+        <v>0.2072679647498543</v>
       </c>
     </row>
     <row r="33" spans="2:4">
       <c r="B33" s="20" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D33" s="22">
-        <v>0.1097518657879768</v>
+        <v>0.1103294112579938</v>
       </c>
     </row>
     <row r="34" spans="2:4">
       <c r="B34" s="20" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D34" s="22">
-        <v>0.09436552567139689</v>
+        <v>0.08695474018993044</v>
       </c>
     </row>
     <row r="35" spans="2:4">
       <c r="B35" s="20" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D35" s="22">
-        <v>0.07950884565368663</v>
+        <v>0.08104838014317833</v>
       </c>
     </row>
     <row r="36" spans="2:4">
       <c r="B36" s="20" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D36" s="22">
-        <v>0.06627784397789481</v>
+        <v>0.06566481648537498</v>
       </c>
     </row>
     <row r="37" spans="2:4">
       <c r="B37" s="20" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D37" s="22">
-        <v>0.06292085307632327</v>
+        <v>0.06502770283897724</v>
       </c>
     </row>
     <row r="38" spans="2:4">
       <c r="B38" s="20" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D38" s="22">
-        <v>0.02805077434430049</v>
+        <v>0.02886063231922146</v>
       </c>
     </row>
     <row r="39" spans="2:4">
       <c r="B39" s="20" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D39" s="22">
-        <v>0.02698732268456907</v>
+        <v>0.02670638510625489</v>
       </c>
     </row>
     <row r="40" spans="2:4">
       <c r="B40" s="20" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D40" s="22">
-        <v>0.01769347382336434</v>
+        <v>0.0182595648196667</v>
       </c>
     </row>
     <row r="41" spans="2:4">
       <c r="B41" s="20" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D41" s="22">
-        <v>0.0119432110315021</v>
+        <v>0.01215077645463919</v>
       </c>
     </row>
     <row r="42" spans="2:4">
       <c r="B42" s="20" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D42" s="22">
-        <v>0.01037383296952268</v>
+        <v>0.01048370974434349</v>
       </c>
     </row>
     <row r="43" spans="2:4">
       <c r="B43" s="20" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D43" s="22">
-        <v>0.002749433326785555</v>
+        <v>0.002736118449849076</v>
       </c>
     </row>
     <row r="44" spans="2:4">
       <c r="B44" s="20" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D44" s="22">
-        <v>0.002008286952367624</v>
+        <v>0.001921939058171737</v>
       </c>
     </row>
     <row r="45" spans="2:4">
       <c r="B45" s="20" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D45" s="22">
         <v>0.0002452424201489956</v>
@@ -2596,13 +2587,13 @@
     </row>
     <row r="46" spans="2:4">
       <c r="B46" s="20" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D46" s="20" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -2981,331 +2972,331 @@
     <row r="9" spans="1:22">
       <c r="A9" s="1"/>
       <c r="B9" s="9" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D9" s="10">
-        <v>0.1540041934261789</v>
+        <v>0.1765740738561665</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="G9" s="12">
-        <v>0.1507458955974199</v>
+        <v>0.1426559076887136</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="J9" s="14">
-        <v>0.129057850082762</v>
+        <v>0.1378001370202004</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="M9" s="16">
-        <v>0.1389344595870833</v>
+        <v>0.1474734223947538</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="P9" s="18">
-        <v>0.2422092101169471</v>
+        <v>0.2432021406964228</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="S9" s="16">
-        <v>0.1029188647058972</v>
+        <v>0.2239663277373959</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="V9" s="18">
-        <v>0.230073021570068</v>
+        <v>0.09762370177294162</v>
       </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1"/>
       <c r="B10" s="9" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D10" s="10">
-        <v>0.08410568250099903</v>
+        <v>0.08711388199983648</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="G10" s="12">
-        <v>0.1183471228528945</v>
+        <v>0.1244660307017811</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="J10" s="14">
-        <v>0.1222367976594496</v>
+        <v>0.1235872990750932</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="M10" s="16">
-        <v>0.1194866454702189</v>
+        <v>0.1177554890690228</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="P10" s="18">
-        <v>0.05854646514656796</v>
+        <v>0.06097960073286671</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="S10" s="16">
-        <v>0.08346369456919076</v>
+        <v>0.07520886862399062</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="V10" s="18">
-        <v>0.08248108907740688</v>
+        <v>0.08865875867510339</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1"/>
       <c r="B11" s="9" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D11" s="10">
-        <v>0.08345872542269725</v>
+        <v>0.08518044417770212</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="G11" s="12">
-        <v>0.07114742558467756</v>
+        <v>0.06253515951372737</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="J11" s="14">
-        <v>0.06740026651975532</v>
+        <v>0.0713895074658783</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="M11" s="16">
-        <v>0.07305499446441936</v>
+        <v>0.07836953471677201</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="P11" s="18">
-        <v>0.05566022797474035</v>
+        <v>0.0562903741540783</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="S11" s="16">
-        <v>0.06149839188636504</v>
+        <v>0.06028550130999383</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="V11" s="18">
-        <v>0.05869451869020115</v>
+        <v>0.05358451666071834</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1"/>
       <c r="B12" s="9" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D12" s="10">
-        <v>0.04858363098026339</v>
+        <v>0.04997503573697654</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="G12" s="12">
-        <v>0.05905286285257654</v>
+        <v>0.05809113395219929</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="J12" s="14">
-        <v>0.06303809003369323</v>
+        <v>0.06637867014304721</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="M12" s="16">
-        <v>0.05142979377395937</v>
+        <v>0.05779928859029715</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="P12" s="18">
-        <v>0.02186825871035256</v>
+        <v>0.02222368564844061</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="S12" s="16">
-        <v>0.04368516858705494</v>
+        <v>0.02559945302289939</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="V12" s="18">
-        <v>0.02340684881789453</v>
+        <v>0.04783375605484786</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1"/>
       <c r="B13" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D13" s="10">
-        <v>0.04424443514143794</v>
+        <v>0.04311544946856531</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="G13" s="12">
-        <v>0.05216142404132922</v>
+        <v>0.04384241013897053</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="J13" s="14">
-        <v>0.0553691457103928</v>
+        <v>0.04480909645555174</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="M13" s="16">
-        <v>0.03193953247213208</v>
+        <v>0.02864579544278929</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="P13" s="18">
-        <v>0.0195179614403234</v>
+        <v>0.0159502628044056</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="S13" s="16">
-        <v>0.03679735847599447</v>
+        <v>0.01924258894948107</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="V13" s="18">
-        <v>0.01877018101982626</v>
+        <v>0.03717551307346097</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -3316,7 +3307,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -3325,7 +3316,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -3334,7 +3325,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -3343,7 +3334,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -3352,7 +3343,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -3361,7 +3352,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -3370,7 +3361,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -3379,331 +3370,331 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="D16" s="10">
-        <v>0.1383825889542535</v>
+        <v>0.1134260399762404</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="G16" s="12">
-        <v>0.1204884220514176</v>
+        <v>0.1252668217424316</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="J16" s="14">
-        <v>0.1362992284276906</v>
+        <v>0.1327767199810578</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="M16" s="16">
-        <v>0.130816403534341</v>
+        <v>0.1216678770943196</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="P16" s="18">
-        <v>0.2512153632421424</v>
+        <v>0.2531952929527964</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="S16" s="16">
-        <v>0.1440774590226259</v>
+        <v>0.3241766839173257</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="V16" s="18">
-        <v>0.3318182604436208</v>
+        <v>0.1427519532777743</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="D17" s="10">
-        <v>0.0716382429010709</v>
+        <v>0.07144578030241087</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="G17" s="12">
-        <v>0.08688377435487017</v>
+        <v>0.09901738343648521</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="J17" s="14">
-        <v>0.1236397444063063</v>
+        <v>0.1277917624099656</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="M17" s="16">
-        <v>0.1134773270340354</v>
+        <v>0.1194423551827162</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="P17" s="18">
-        <v>0.1012938844014975</v>
+        <v>0.1013785529121582</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="S17" s="16">
-        <v>0.1187070172596411</v>
+        <v>0.06104638427164618</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="V17" s="18">
-        <v>0.06277442594563902</v>
+        <v>0.1191671047852329</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="D18" s="10">
-        <v>0.06366013871117089</v>
+        <v>0.06233264056069518</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="G18" s="12">
-        <v>0.06011543452533127</v>
+        <v>0.04974546852764734</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="J18" s="14">
-        <v>0.04988796777306103</v>
+        <v>0.04328914840483299</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="M18" s="16">
-        <v>0.07203010641554053</v>
+        <v>0.07318438594049796</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="P18" s="18">
-        <v>0.06250575145592252</v>
+        <v>0.06111481111252803</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="S18" s="16">
-        <v>0.05784985640131127</v>
+        <v>0.05828168821160529</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="V18" s="18">
-        <v>0.05423439843893411</v>
+        <v>0.0594087781929989</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D19" s="10">
-        <v>0.06079801997620607</v>
+        <v>0.0527053564675671</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="G19" s="12">
-        <v>0.04481390283899574</v>
+        <v>0.04841134924653776</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="J19" s="14">
-        <v>0.03662491140774583</v>
+        <v>0.0406110060505251</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="M19" s="16">
-        <v>0.04973157535316139</v>
+        <v>0.03981304885557774</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="P19" s="18">
-        <v>0.04394924099461872</v>
+        <v>0.04644595622724425</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="S19" s="16">
-        <v>0.04134274614814771</v>
+        <v>0.02142636029335716</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="V19" s="18">
-        <v>0.02042545768949635</v>
+        <v>0.03994382859994369</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="D20" s="10">
-        <v>0.05384274117989196</v>
+        <v>0.05106021083534705</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G20" s="12">
-        <v>0.03728348934623885</v>
+        <v>0.0415505629844608</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="J20" s="14">
-        <v>0.02065614866790612</v>
+        <v>0.02540960989212542</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="M20" s="16">
-        <v>0.03727529246185941</v>
+        <v>0.0283969306578588</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="P20" s="18">
-        <v>0.03148747196221306</v>
+        <v>0.03112508678285477</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="R20" s="15" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="S20" s="16">
-        <v>0.03287351132057185</v>
+        <v>0.01697301346580545</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="V20" s="18">
-        <v>0.01673344531051994</v>
+        <v>0.03301404695156723</v>
       </c>
     </row>
   </sheetData>
